--- a/docs/IMA_Progress.xlsx
+++ b/docs/IMA_Progress.xlsx
@@ -4,22 +4,566 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="KPI" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Phase" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Sections" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Variance" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Milestones" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="Engineering" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Procurement" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="SCurve" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="WPInfo" state="visible" r:id="rId12"/>
+    <sheet sheetId="1" name="README" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="ENG" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="FAB" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="LOG" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="SITE" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="COMM" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="HSE" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="Procurement" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="Milestones" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="KPI" state="hidden" r:id="rId13"/>
+    <sheet sheetId="11" name="Phase" state="hidden" r:id="rId14"/>
+    <sheet sheetId="12" name="Sections" state="hidden" r:id="rId15"/>
+    <sheet sheetId="13" name="Variance" state="hidden" r:id="rId16"/>
+    <sheet sheetId="14" name="Engineering" state="hidden" r:id="rId17"/>
+    <sheet sheetId="15" name="SCurve" state="hidden" r:id="rId18"/>
+    <sheet sheetId="16" name="WPInfo" state="hidden" r:id="rId19"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="420">
+  <si>
+    <t>IMA BROWNFIELD — EPCI PROGRESS WORKBOOK</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Cách dùng:</t>
+  </si>
+  <si>
+    <t>1. Mỗi discipline có 1 sheet log task: ENG, FAB, LOG, SITE, COMM. Nhập task vào, điền Weight % và % Complete.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Ô "Auto %" (góc trên, màu xanh) tự tính tiến độ Actual của discipline = Σ(Weight×%Complete)/ΣWeight.</t>
+  </si>
+  <si>
+    <t>2. Procurement: list 16 package — cập nhật cột Prog (0–100) và các mốc PO / FAT / Site.</t>
+  </si>
+  <si>
+    <t>3. HSE: log theo tuần (manhours, LTI, observations, NCR).</t>
+  </si>
+  <si>
+    <t>4. Milestones: cập nhật Forecast + Status các Key Date.</t>
+  </si>
+  <si>
+    <t>Cập nhật hằng tuần (giữ trend trên web):</t>
+  </si>
+  <si>
+    <t>Cuối tuần: ở các sheet ẩn KPI/Phase/Sections, copy cột tuần hiện tại → Paste special → Values only (chốt số),</t>
+  </si>
+  <si>
+    <t>rồi thêm cột tuần mới (vd Wk67) sao chép công thức tuần cũ. Web vẽ trend qua các tuần đã chốt.</t>
+  </si>
+  <si>
+    <t>Sheet ẩn (KPI, Phase, Sections, Variance, Engineering, SCurve, WPInfo) = dữ liệu web đọc.</t>
+  </si>
+  <si>
+    <t>KHÔNG sửa tay trừ các ô đếm/KPI (PO, NCR, punch, manhours…). Bỏ ẩn: chuột phải tab → Unhide.</t>
+  </si>
+  <si>
+    <t>Đẩy lên web: Share → Anyone with the link → Viewer. Copy Spreadsheet ID (đoạn /d/&lt;ID&gt;/edit) → đặt SHEETS_ID.</t>
+  </si>
+  <si>
+    <t>Chi tiết: docs/BACKEND_SETUP.md §F–H. Số sửa trong Sheet → web tự cập nhật ≤ 5 phút.</t>
+  </si>
+  <si>
+    <t>Engineering  —  Auto % (Actual, current week):</t>
+  </si>
+  <si>
+    <t>◀ tự tính từ Weight × % Complete</t>
+  </si>
+  <si>
+    <t>WBS / ID</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Weight %</t>
+  </si>
+  <si>
+    <t>Plan Start</t>
+  </si>
+  <si>
+    <t>Plan Finish</t>
+  </si>
+  <si>
+    <t>Actual Start</t>
+  </si>
+  <si>
+    <t>Actual Finish</t>
+  </si>
+  <si>
+    <t>% Complete</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Responsible</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>ENG-001</t>
+  </si>
+  <si>
+    <t>IFC drawings — Process &amp; Mechanical</t>
+  </si>
+  <si>
+    <t>01-Jul-2026</t>
+  </si>
+  <si>
+    <t>30-Jun-2028</t>
+  </si>
+  <si>
+    <t>Complete</t>
+  </si>
+  <si>
+    <t>PTSC</t>
+  </si>
+  <si>
+    <t>Process</t>
+  </si>
+  <si>
+    <t>ENG-002</t>
+  </si>
+  <si>
+    <t>IFC drawings — Piping &amp; Layout</t>
+  </si>
+  <si>
+    <t>Piping &amp; Layout</t>
+  </si>
+  <si>
+    <t>ENG-003</t>
+  </si>
+  <si>
+    <t>IFC drawings — Electrical &amp; Instrument</t>
+  </si>
+  <si>
+    <t>Electrical/Instrument</t>
+  </si>
+  <si>
+    <t>ENG-004</t>
+  </si>
+  <si>
+    <t>As-built &amp; engineering close-out</t>
+  </si>
+  <si>
+    <t>Comm. Eng.</t>
+  </si>
+  <si>
+    <t>Fabrication  —  Auto % (Actual, current week):</t>
+  </si>
+  <si>
+    <t>Welds</t>
+  </si>
+  <si>
+    <t>NDT %</t>
+  </si>
+  <si>
+    <t>Tonnage (T)</t>
+  </si>
+  <si>
+    <t>FAB-001</t>
+  </si>
+  <si>
+    <t>Structural fabrication</t>
+  </si>
+  <si>
+    <t>FAB-002</t>
+  </si>
+  <si>
+    <t>Piping spool fabrication</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>FAB-003</t>
+  </si>
+  <si>
+    <t>Equipment skid assembly</t>
+  </si>
+  <si>
+    <t>FAB-004</t>
+  </si>
+  <si>
+    <t>Surface treatment &amp; painting</t>
+  </si>
+  <si>
+    <t>Logistics &amp; Transport  —  Auto % (Actual, current week):</t>
+  </si>
+  <si>
+    <t>MWS</t>
+  </si>
+  <si>
+    <t>Weight (T)</t>
+  </si>
+  <si>
+    <t>LOG-001</t>
+  </si>
+  <si>
+    <t>Sea-fastening &amp; grillage design</t>
+  </si>
+  <si>
+    <t>4 / 4</t>
+  </si>
+  <si>
+    <t>LOG-002</t>
+  </si>
+  <si>
+    <t>Load-out engineering</t>
+  </si>
+  <si>
+    <t>LOG-003</t>
+  </si>
+  <si>
+    <t>Transport / MWS mobilization</t>
+  </si>
+  <si>
+    <t>LOG-004</t>
+  </si>
+  <si>
+    <t>Offshore installation</t>
+  </si>
+  <si>
+    <t>Site Construction  —  Auto % (Actual, current week):</t>
+  </si>
+  <si>
+    <t>Tie-in Done</t>
+  </si>
+  <si>
+    <t>Tie-in Total</t>
+  </si>
+  <si>
+    <t>PTW</t>
+  </si>
+  <si>
+    <t>SITE-001</t>
+  </si>
+  <si>
+    <t>Civil works &amp; foundations</t>
+  </si>
+  <si>
+    <t>SITE-002</t>
+  </si>
+  <si>
+    <t>Structural steel erection</t>
+  </si>
+  <si>
+    <t>SITE-003</t>
+  </si>
+  <si>
+    <t>Mechanical / piping installation</t>
+  </si>
+  <si>
+    <t>SITE-004</t>
+  </si>
+  <si>
+    <t>E&amp;I installation &amp; tie-ins</t>
+  </si>
+  <si>
+    <t>Commissioning  —  Auto % (Actual, current week):</t>
+  </si>
+  <si>
+    <t>System</t>
+  </si>
+  <si>
+    <t>Punch</t>
+  </si>
+  <si>
+    <t>COMM-001</t>
+  </si>
+  <si>
+    <t>Pre-commissioning preparation</t>
+  </si>
+  <si>
+    <t>COMM-002</t>
+  </si>
+  <si>
+    <t>System walkdowns</t>
+  </si>
+  <si>
+    <t>Utilities</t>
+  </si>
+  <si>
+    <t>COMM-003</t>
+  </si>
+  <si>
+    <t>Loop checks &amp; function tests</t>
+  </si>
+  <si>
+    <t>Not Started</t>
+  </si>
+  <si>
+    <t>Safety</t>
+  </si>
+  <si>
+    <t>COMM-004</t>
+  </si>
+  <si>
+    <t>Start-up &amp; performance test</t>
+  </si>
+  <si>
+    <t>Week</t>
+  </si>
+  <si>
+    <t>Safe Manhours</t>
+  </si>
+  <si>
+    <t>LTI</t>
+  </si>
+  <si>
+    <t>Observations</t>
+  </si>
+  <si>
+    <t>NCR</t>
+  </si>
+  <si>
+    <t>Comment</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>1,210K</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>1,250K</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>1,310K</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>PO</t>
+  </si>
+  <si>
+    <t>FAT</t>
+  </si>
+  <si>
+    <t>Site</t>
+  </si>
+  <si>
+    <t>Prog</t>
+  </si>
+  <si>
+    <t>Pig Receiver (AA-8133)</t>
+  </si>
+  <si>
+    <t>30-Sep-2026</t>
+  </si>
+  <si>
+    <t>01-Sep-2027</t>
+  </si>
+  <si>
+    <t>30-Nov-2027</t>
+  </si>
+  <si>
+    <t>Slug Catcher (V-8133)</t>
+  </si>
+  <si>
+    <t>31-Aug-2026</t>
+  </si>
+  <si>
+    <t>TEG Package (C-8160 / A-8160)</t>
+  </si>
+  <si>
+    <t>31-Oct-2027</t>
+  </si>
+  <si>
+    <t>29-Jan-2028</t>
+  </si>
+  <si>
+    <t>Mercury Removal Unit (A-8170)</t>
+  </si>
+  <si>
+    <t>01-Sep-2026</t>
+  </si>
+  <si>
+    <t>01-Nov-2027</t>
+  </si>
+  <si>
+    <t>30-Jan-2028</t>
+  </si>
+  <si>
+    <t>ICSS Cabinets</t>
+  </si>
+  <si>
+    <t>02-Aug-2027</t>
+  </si>
+  <si>
+    <t>16-Sep-2027</t>
+  </si>
+  <si>
+    <t>Gas Fiscal Metering (M-8101)</t>
+  </si>
+  <si>
+    <t>HIPPS Package</t>
+  </si>
+  <si>
+    <t>HV Switchboard</t>
+  </si>
+  <si>
+    <t>13-Jun-2027</t>
+  </si>
+  <si>
+    <t>28-Jul-2027</t>
+  </si>
+  <si>
+    <t>Electrical Room</t>
+  </si>
+  <si>
+    <t>30-Oct-2027</t>
+  </si>
+  <si>
+    <t>28-Jan-2028</t>
+  </si>
+  <si>
+    <t>Instrument Room</t>
+  </si>
+  <si>
+    <t>HP Separator (V-8151)</t>
+  </si>
+  <si>
+    <t>30-Nov-2026</t>
+  </si>
+  <si>
+    <t>26-Sep-2027</t>
+  </si>
+  <si>
+    <t>25-Dec-2027</t>
+  </si>
+  <si>
+    <t>Condensate Pump A/B (P-8151)</t>
+  </si>
+  <si>
+    <t>31-Dec-2026</t>
+  </si>
+  <si>
+    <t>29-Jul-2027</t>
+  </si>
+  <si>
+    <t>27-Oct-2027</t>
+  </si>
+  <si>
+    <t>Water Pump A/B (P-8152)</t>
+  </si>
+  <si>
+    <t>Condensate Metering (M-8102)</t>
+  </si>
+  <si>
+    <t>01-Oct-2027</t>
+  </si>
+  <si>
+    <t>30-Dec-2027</t>
+  </si>
+  <si>
+    <t>Water Metering Skid (M-8103)</t>
+  </si>
+  <si>
+    <t>Flow Control Station (FCV-332)</t>
+  </si>
+  <si>
+    <t>22-Oct-2027</t>
+  </si>
+  <si>
+    <t>Baseline</t>
+  </si>
+  <si>
+    <t>Forecast</t>
+  </si>
+  <si>
+    <t>KD 01 - Effective Date (ED)</t>
+  </si>
+  <si>
+    <t>completed</t>
+  </si>
+  <si>
+    <t>KD 02 - KOM &amp; Key Personnel Mobilized</t>
+  </si>
+  <si>
+    <t>08-Jul-2026</t>
+  </si>
+  <si>
+    <t>KD 07 - Detailed Work Plan Approved</t>
+  </si>
+  <si>
+    <t>30-Jul-2026</t>
+  </si>
+  <si>
+    <t>KD 10-13 - PO for Major Packages Placed</t>
+  </si>
+  <si>
+    <t>KD 16 - Detailed Engineering 50% IFC</t>
+  </si>
+  <si>
+    <t>15-Dec-2026</t>
+  </si>
+  <si>
+    <t>KD 17 - TCC Earthworks &amp; Foundations</t>
+  </si>
+  <si>
+    <t>13-Feb-2027</t>
+  </si>
+  <si>
+    <t>KD 18 - Detailed Engineering 100% IFC</t>
+  </si>
+  <si>
+    <t>01-Jun-2027</t>
+  </si>
+  <si>
+    <t>KD 20 - TCC Readiness Certificate</t>
+  </si>
+  <si>
+    <t>30-Jun-2027</t>
+  </si>
+  <si>
+    <t>KD 21 - Slug Catcher Delivered to SITE</t>
+  </si>
+  <si>
+    <t>01-Dec-2027</t>
+  </si>
+  <si>
+    <t>not-started</t>
+  </si>
+  <si>
+    <t>KD 22 - TEG Unit Delivered to SITE</t>
+  </si>
+  <si>
+    <t>KD 23 - Metering Unit Delivered to SITE</t>
+  </si>
+  <si>
+    <t>KD 24 - Functional Ready for Commissioning</t>
+  </si>
+  <si>
+    <t>05-May-2028</t>
+  </si>
+  <si>
+    <t>KD 27 - Provisional Acceptance Certificate</t>
+  </si>
+  <si>
+    <t>03-Jan-2029</t>
+  </si>
   <si>
     <t>Metric</t>
   </si>
@@ -90,15 +634,6 @@
     <t>sum_kpi_hse</t>
   </si>
   <si>
-    <t>1,210K</t>
-  </si>
-  <si>
-    <t>1,250K</t>
-  </si>
-  <si>
-    <t>1,310K</t>
-  </si>
-  <si>
     <t>sum_kpi_risks</t>
   </si>
   <si>
@@ -276,9 +811,6 @@
     <t>90.0%</t>
   </si>
   <si>
-    <t>93.0%</t>
-  </si>
-  <si>
     <t>fabrication.prog_vs</t>
   </si>
   <si>
@@ -336,18 +868,12 @@
     <t>45.0%</t>
   </si>
   <si>
-    <t>48.0%</t>
-  </si>
-  <si>
     <t>logistics.mws</t>
   </si>
   <si>
     <t>3 / 4</t>
   </si>
   <si>
-    <t>4 / 4</t>
-  </si>
-  <si>
     <t>logistics.weight</t>
   </si>
   <si>
@@ -366,9 +892,6 @@
     <t>27.8%</t>
   </si>
   <si>
-    <t>30.5%</t>
-  </si>
-  <si>
     <t>site.prog_vs</t>
   </si>
   <si>
@@ -420,9 +943,6 @@
     <t>1.0%</t>
   </si>
   <si>
-    <t>3.0%</t>
-  </si>
-  <si>
     <t>commissioning.sys</t>
   </si>
   <si>
@@ -474,9 +994,6 @@
     <t>hse.ncr</t>
   </si>
   <si>
-    <t>Week</t>
-  </si>
-  <si>
     <t>V1</t>
   </si>
   <si>
@@ -516,120 +1033,12 @@
     <t>V13</t>
   </si>
   <si>
-    <t>64</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>66</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Baseline</t>
-  </si>
-  <si>
-    <t>Forecast</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>KD 01 - Effective Date (ED)</t>
-  </si>
-  <si>
-    <t>01-Jul-2026</t>
-  </si>
-  <si>
-    <t>completed</t>
-  </si>
-  <si>
-    <t>KD 02 - KOM &amp; Key Personnel Mobilized</t>
-  </si>
-  <si>
-    <t>08-Jul-2026</t>
-  </si>
-  <si>
-    <t>KD 07 - Detailed Work Plan Approved</t>
-  </si>
-  <si>
-    <t>30-Jul-2026</t>
-  </si>
-  <si>
-    <t>KD 10-13 - PO for Major Packages Placed</t>
-  </si>
-  <si>
-    <t>31-Aug-2026</t>
-  </si>
-  <si>
-    <t>KD 16 - Detailed Engineering 50% IFC</t>
-  </si>
-  <si>
-    <t>15-Dec-2026</t>
-  </si>
-  <si>
-    <t>KD 17 - TCC Earthworks &amp; Foundations</t>
-  </si>
-  <si>
-    <t>13-Feb-2027</t>
-  </si>
-  <si>
-    <t>KD 18 - Detailed Engineering 100% IFC</t>
-  </si>
-  <si>
-    <t>01-Jun-2027</t>
-  </si>
-  <si>
-    <t>KD 20 - TCC Readiness Certificate</t>
-  </si>
-  <si>
-    <t>30-Jun-2027</t>
-  </si>
-  <si>
-    <t>KD 21 - Slug Catcher Delivered to SITE</t>
-  </si>
-  <si>
-    <t>01-Dec-2027</t>
-  </si>
-  <si>
-    <t>not-started</t>
-  </si>
-  <si>
-    <t>KD 22 - TEG Unit Delivered to SITE</t>
-  </si>
-  <si>
-    <t>29-Jan-2028</t>
-  </si>
-  <si>
-    <t>KD 23 - Metering Unit Delivered to SITE</t>
-  </si>
-  <si>
-    <t>KD 24 - Functional Ready for Commissioning</t>
-  </si>
-  <si>
-    <t>05-May-2028</t>
-  </si>
-  <si>
-    <t>KD 27 - Provisional Acceptance Certificate</t>
-  </si>
-  <si>
-    <t>03-Jan-2029</t>
-  </si>
-  <si>
     <t>Actual</t>
   </si>
   <si>
     <t>Target</t>
   </si>
   <si>
-    <t>Process</t>
-  </si>
-  <si>
-    <t>Piping &amp; Layout</t>
-  </si>
-  <si>
     <t>Mechanical</t>
   </si>
   <si>
@@ -651,135 +1060,6 @@
     <t>Telecom</t>
   </si>
   <si>
-    <t>Comm. Eng.</t>
-  </si>
-  <si>
-    <t>PO</t>
-  </si>
-  <si>
-    <t>FAT</t>
-  </si>
-  <si>
-    <t>Site</t>
-  </si>
-  <si>
-    <t>Prog</t>
-  </si>
-  <si>
-    <t>Pig Receiver (AA-8133)</t>
-  </si>
-  <si>
-    <t>30-Sep-2026</t>
-  </si>
-  <si>
-    <t>01-Sep-2027</t>
-  </si>
-  <si>
-    <t>30-Nov-2027</t>
-  </si>
-  <si>
-    <t>Slug Catcher (V-8133)</t>
-  </si>
-  <si>
-    <t>TEG Package (C-8160 / A-8160)</t>
-  </si>
-  <si>
-    <t>31-Oct-2027</t>
-  </si>
-  <si>
-    <t>Mercury Removal Unit (A-8170)</t>
-  </si>
-  <si>
-    <t>01-Sep-2026</t>
-  </si>
-  <si>
-    <t>01-Nov-2027</t>
-  </si>
-  <si>
-    <t>30-Jan-2028</t>
-  </si>
-  <si>
-    <t>ICSS Cabinets</t>
-  </si>
-  <si>
-    <t>02-Aug-2027</t>
-  </si>
-  <si>
-    <t>16-Sep-2027</t>
-  </si>
-  <si>
-    <t>Gas Fiscal Metering (M-8101)</t>
-  </si>
-  <si>
-    <t>HIPPS Package</t>
-  </si>
-  <si>
-    <t>HV Switchboard</t>
-  </si>
-  <si>
-    <t>13-Jun-2027</t>
-  </si>
-  <si>
-    <t>28-Jul-2027</t>
-  </si>
-  <si>
-    <t>Electrical Room</t>
-  </si>
-  <si>
-    <t>30-Oct-2027</t>
-  </si>
-  <si>
-    <t>28-Jan-2028</t>
-  </si>
-  <si>
-    <t>Instrument Room</t>
-  </si>
-  <si>
-    <t>HP Separator (V-8151)</t>
-  </si>
-  <si>
-    <t>30-Nov-2026</t>
-  </si>
-  <si>
-    <t>26-Sep-2027</t>
-  </si>
-  <si>
-    <t>25-Dec-2027</t>
-  </si>
-  <si>
-    <t>Condensate Pump A/B (P-8151)</t>
-  </si>
-  <si>
-    <t>31-Dec-2026</t>
-  </si>
-  <si>
-    <t>29-Jul-2027</t>
-  </si>
-  <si>
-    <t>27-Oct-2027</t>
-  </si>
-  <si>
-    <t>Water Pump A/B (P-8152)</t>
-  </si>
-  <si>
-    <t>Condensate Metering (M-8102)</t>
-  </si>
-  <si>
-    <t>01-Oct-2027</t>
-  </si>
-  <si>
-    <t>30-Dec-2027</t>
-  </si>
-  <si>
-    <t>Water Metering Skid (M-8103)</t>
-  </si>
-  <si>
-    <t>Flow Control Station (FCV-332)</t>
-  </si>
-  <si>
-    <t>22-Oct-2027</t>
-  </si>
-  <si>
     <t>Month</t>
   </si>
   <si>
@@ -829,9 +1109,6 @@
   </si>
   <si>
     <t>Jun-26</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>Jul-26</t>
@@ -1015,7 +1292,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1025,16 +1302,40 @@
     </font>
     <font>
       <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
+      <color rgb="FF24397A"/>
+      <sz val="16"/>
       <name val="Times New Roman"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Times New Roman"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FF24397A"/>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF1565C0"/>
+      <sz val="14"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF888888"/>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1043,11 +1344,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFEAF6FD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF24397A"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1055,16 +1361,44 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBBC6DD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBBC6DD"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBBC6DD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBBC6DD"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1083,7 +1417,45 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" name="KPI" displayName="KPI" ref="A1:D13" totalsRowShown="1" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" name="Procurement" displayName="Procurement" ref="A1:E17" totalsRowShown="1" headerRowCount="1">
+  <autoFilter ref="A1:E17">
+    <filterColumn colId="0" hiddenButton="0"/>
+    <filterColumn colId="1" hiddenButton="0"/>
+    <filterColumn colId="2" hiddenButton="0"/>
+    <filterColumn colId="3" hiddenButton="0"/>
+    <filterColumn colId="4" hiddenButton="0"/>
+  </autoFilter>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Name" totalsRowLabel="Total"/>
+    <tableColumn id="2" name="PO" totalsRowFunction="none"/>
+    <tableColumn id="3" name="FAT" totalsRowFunction="none"/>
+    <tableColumn id="4" name="Site" totalsRowFunction="none"/>
+    <tableColumn id="5" name="Prog" totalsRowFunction="none"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" name="Milestones" displayName="Milestones" ref="A1:D14" totalsRowShown="1" headerRowCount="1">
+  <autoFilter ref="A1:D14">
+    <filterColumn colId="0" hiddenButton="0"/>
+    <filterColumn colId="1" hiddenButton="0"/>
+    <filterColumn colId="2" hiddenButton="0"/>
+    <filterColumn colId="3" hiddenButton="0"/>
+  </autoFilter>
+  <tableColumns count="4">
+    <tableColumn id="1" name="Name" totalsRowLabel="Total"/>
+    <tableColumn id="2" name="Baseline" totalsRowFunction="none"/>
+    <tableColumn id="3" name="Forecast" totalsRowFunction="none"/>
+    <tableColumn id="4" name="Status" totalsRowFunction="none"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" name="KPI" displayName="KPI" ref="A1:D13" totalsRowShown="1" headerRowCount="1">
   <autoFilter ref="A1:D13">
     <filterColumn colId="0" hiddenButton="0"/>
     <filterColumn colId="1" hiddenButton="0"/>
@@ -1100,8 +1472,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" name="Phase" displayName="Phase" ref="A1:G7" totalsRowShown="1" headerRowCount="1">
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" name="Phase" displayName="Phase" ref="A1:G7" totalsRowShown="1" headerRowCount="1">
   <autoFilter ref="A1:G7">
     <filterColumn colId="0" hiddenButton="0"/>
     <filterColumn colId="1" hiddenButton="0"/>
@@ -1124,8 +1496,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" name="Sections" displayName="Sections" ref="A1:D35" totalsRowShown="1" headerRowCount="1">
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" name="Sections" displayName="Sections" ref="A1:D35" totalsRowShown="1" headerRowCount="1">
   <autoFilter ref="A1:D35">
     <filterColumn colId="0" hiddenButton="0"/>
     <filterColumn colId="1" hiddenButton="0"/>
@@ -1142,8 +1514,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" name="Variance" displayName="Variance" ref="A1:N4" totalsRowShown="1" headerRowCount="1">
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" name="Variance" displayName="Variance" ref="A1:N4" totalsRowShown="1" headerRowCount="1">
   <autoFilter ref="A1:N4">
     <filterColumn colId="0" hiddenButton="0"/>
     <filterColumn colId="1" hiddenButton="0"/>
@@ -1180,26 +1552,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" name="Milestones" displayName="Milestones" ref="A1:D14" totalsRowShown="1" headerRowCount="1">
-  <autoFilter ref="A1:D14">
-    <filterColumn colId="0" hiddenButton="0"/>
-    <filterColumn colId="1" hiddenButton="0"/>
-    <filterColumn colId="2" hiddenButton="0"/>
-    <filterColumn colId="3" hiddenButton="0"/>
-  </autoFilter>
-  <tableColumns count="4">
-    <tableColumn id="1" name="Name" totalsRowLabel="Total"/>
-    <tableColumn id="2" name="Baseline" totalsRowFunction="none"/>
-    <tableColumn id="3" name="Forecast" totalsRowFunction="none"/>
-    <tableColumn id="4" name="Status" totalsRowFunction="none"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" name="Engineering" displayName="Engineering" ref="A1:D11" totalsRowShown="1" headerRowCount="1">
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" name="Engineering" displayName="Engineering" ref="A1:D11" totalsRowShown="1" headerRowCount="1">
   <autoFilter ref="A1:D11">
     <filterColumn colId="0" hiddenButton="0"/>
     <filterColumn colId="1" hiddenButton="0"/>
@@ -1211,26 +1565,6 @@
     <tableColumn id="2" name="Actual" totalsRowFunction="none"/>
     <tableColumn id="3" name="Target" totalsRowFunction="none"/>
     <tableColumn id="4" name="Status" totalsRowFunction="none"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" name="Procurement" displayName="Procurement" ref="A1:E17" totalsRowShown="1" headerRowCount="1">
-  <autoFilter ref="A1:E17">
-    <filterColumn colId="0" hiddenButton="0"/>
-    <filterColumn colId="1" hiddenButton="0"/>
-    <filterColumn colId="2" hiddenButton="0"/>
-    <filterColumn colId="3" hiddenButton="0"/>
-    <filterColumn colId="4" hiddenButton="0"/>
-  </autoFilter>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Name" totalsRowLabel="Total"/>
-    <tableColumn id="2" name="PO" totalsRowFunction="none"/>
-    <tableColumn id="3" name="FAT" totalsRowFunction="none"/>
-    <tableColumn id="4" name="Site" totalsRowFunction="none"/>
-    <tableColumn id="5" name="Prog" totalsRowFunction="none"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1616,6 +1950,111 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:B18"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="110" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B4" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B6" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B8" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B9" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B10" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B11" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B12" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B13" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B14" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B15" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B16" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -1624,185 +2063,185 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
+      <c r="A1" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>183</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
+        <v>184</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>5</v>
+        <v>184</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>5</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>6</v>
+        <v>185</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>7</v>
+        <v>186</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>7</v>
+        <v>186</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>7</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>8</v>
+        <v>187</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>9</v>
+        <v>188</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>188</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>9</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>10</v>
+        <v>189</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>11</v>
+        <v>190</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>12</v>
+        <v>191</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>13</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>193</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>15</v>
+        <v>194</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>16</v>
+        <v>195</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>17</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>18</v>
+        <v>197</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>19</v>
+        <v>198</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>20</v>
+        <v>199</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>21</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>22</v>
+        <v>201</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>23</v>
+        <v>103</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>24</v>
+        <v>105</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>25</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>26</v>
+        <v>202</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>27</v>
+        <v>203</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>28</v>
+        <v>204</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>28</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>29</v>
+        <v>205</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>30</v>
+        <v>206</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>28</v>
+        <v>204</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>28</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>31</v>
+        <v>207</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>32</v>
+        <v>208</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>33</v>
+        <v>209</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>35</v>
+        <v>211</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>36</v>
+        <v>212</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>30</v>
+        <v>206</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>27</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>37</v>
+        <v>213</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>38</v>
+        <v>214</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>39</v>
+        <v>215</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>40</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>
@@ -1814,7 +2253,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -1824,31 +2263,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>47</v>
+      <c r="A1" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>48</v>
+        <v>224</v>
       </c>
       <c r="B2" s="2">
         <v>100</v>
@@ -1866,12 +2305,13 @@
         <v>100</v>
       </c>
       <c r="G2" s="2">
+        <f>ENG!B1</f>
         <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>49</v>
+        <v>225</v>
       </c>
       <c r="B3" s="2">
         <v>83.5</v>
@@ -1894,7 +2334,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>50</v>
+        <v>226</v>
       </c>
       <c r="B4" s="2">
         <v>85</v>
@@ -1912,12 +2352,13 @@
         <v>91</v>
       </c>
       <c r="G4" s="2">
+        <f>FAB!B1</f>
         <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>51</v>
+        <v>227</v>
       </c>
       <c r="B5" s="2">
         <v>40</v>
@@ -1935,12 +2376,13 @@
         <v>46</v>
       </c>
       <c r="G5" s="2">
+        <f>LOG!B1</f>
         <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>52</v>
+        <v>228</v>
       </c>
       <c r="B6" s="2">
         <v>23</v>
@@ -1958,12 +2400,13 @@
         <v>28</v>
       </c>
       <c r="G6" s="2">
+        <f>SITE!B1</f>
         <v>30.5</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>53</v>
+        <v>229</v>
       </c>
       <c r="B7" s="2">
         <v>0</v>
@@ -1981,6 +2424,7 @@
         <v>2</v>
       </c>
       <c r="G7" s="2">
+        <f>COMM!B1</f>
         <v>3</v>
       </c>
     </row>
@@ -1993,7 +2437,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -2003,493 +2447,498 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
+      <c r="A1" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>55</v>
+        <v>231</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>56</v>
+        <v>232</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>56</v>
+        <v>232</v>
+      </c>
+      <c r="D2" s="2" t="str">
+        <f>TEXT(ENG!B1,"0.0")&amp;"%"</f>
+        <v>100.0%</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>57</v>
+        <v>233</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>58</v>
+        <v>234</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>58</v>
+        <v>234</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>58</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>59</v>
+        <v>235</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>60</v>
+        <v>236</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>60</v>
+        <v>236</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>60</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>61</v>
+        <v>237</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>62</v>
+        <v>238</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>62</v>
+        <v>238</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>62</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>63</v>
+        <v>239</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>56</v>
+        <v>232</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>56</v>
+        <v>232</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>56</v>
+        <v>232</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>64</v>
+        <v>240</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>65</v>
+        <v>241</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>65</v>
+        <v>241</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>65</v>
+        <v>241</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>66</v>
+        <v>242</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>28</v>
+        <v>204</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>28</v>
+        <v>204</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>28</v>
+        <v>204</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>67</v>
+        <v>243</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>68</v>
+        <v>244</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>69</v>
+        <v>245</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>70</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>71</v>
+        <v>247</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>72</v>
+        <v>248</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>73</v>
+        <v>249</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>74</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>75</v>
+        <v>251</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>76</v>
+        <v>252</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>76</v>
+        <v>252</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>76</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>77</v>
+        <v>253</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>78</v>
+        <v>254</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>79</v>
+        <v>255</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>80</v>
+        <v>256</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>81</v>
+        <v>257</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>28</v>
+        <v>204</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>28</v>
+        <v>204</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>28</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>82</v>
+        <v>258</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>83</v>
+        <v>259</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>85</v>
+        <v>260</v>
+      </c>
+      <c r="D14" s="2" t="str">
+        <f>TEXT(FAB!B1,"0.0")&amp;"%"</f>
+        <v>93.0%</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>86</v>
+        <v>261</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>87</v>
+        <v>262</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>88</v>
+        <v>263</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>89</v>
+        <v>264</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>90</v>
+        <v>265</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>91</v>
+        <v>266</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>92</v>
+        <v>267</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>93</v>
+        <v>268</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>94</v>
+        <v>269</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>95</v>
+        <v>270</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>96</v>
+        <v>271</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>97</v>
+        <v>272</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>98</v>
+        <v>273</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>99</v>
+        <v>274</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>100</v>
+        <v>275</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>101</v>
+        <v>276</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>102</v>
+        <v>277</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>103</v>
+        <v>278</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>105</v>
+        <v>279</v>
+      </c>
+      <c r="D19" s="2" t="str">
+        <f>TEXT(LOG!B1,"0.0")&amp;"%"</f>
+        <v>48.0%</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>106</v>
+        <v>280</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>107</v>
+        <v>281</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>108</v>
+        <v>63</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>108</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>109</v>
+        <v>282</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>110</v>
+        <v>283</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>110</v>
+        <v>283</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>110</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>111</v>
+        <v>284</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>28</v>
+        <v>204</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>28</v>
+        <v>204</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>28</v>
+        <v>204</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>112</v>
+        <v>285</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>113</v>
+        <v>286</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>115</v>
+        <v>287</v>
+      </c>
+      <c r="D23" s="2" t="str">
+        <f>TEXT(SITE!B1,"0.0")&amp;"%"</f>
+        <v>30.5%</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>116</v>
+        <v>288</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>117</v>
+        <v>289</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>118</v>
+        <v>290</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>119</v>
+        <v>291</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>120</v>
+        <v>292</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>121</v>
+        <v>293</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>122</v>
+        <v>294</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>123</v>
+        <v>295</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>124</v>
+        <v>296</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>125</v>
+        <v>297</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>125</v>
+        <v>297</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>125</v>
+        <v>297</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>126</v>
+        <v>298</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>127</v>
+        <v>299</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>128</v>
+        <v>300</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>129</v>
+        <v>301</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>130</v>
+        <v>302</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>131</v>
+        <v>303</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>133</v>
+        <v>304</v>
+      </c>
+      <c r="D28" s="2" t="str">
+        <f>TEXT(COMM!B1,"0.0")&amp;"%"</f>
+        <v>3.0%</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>134</v>
+        <v>305</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>135</v>
+        <v>306</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>135</v>
+        <v>306</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>135</v>
+        <v>306</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>136</v>
+        <v>307</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>137</v>
+        <v>308</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>138</v>
+        <v>309</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>139</v>
+        <v>310</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>140</v>
+        <v>311</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>38</v>
+        <v>214</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>39</v>
+        <v>215</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>40</v>
+        <v>216</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>141</v>
+        <v>312</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>28</v>
+        <v>204</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>28</v>
+        <v>204</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>28</v>
+        <v>204</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>142</v>
+        <v>313</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>143</v>
+        <v>314</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>144</v>
+        <v>315</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>145</v>
+        <v>316</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>146</v>
+        <v>317</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>147</v>
+        <v>318</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>148</v>
+        <v>319</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>149</v>
+        <v>320</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>150</v>
+        <v>321</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>36</v>
+        <v>212</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>30</v>
+        <v>206</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>27</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -2501,7 +2950,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -2511,52 +2960,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>164</v>
+      <c r="A1" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>165</v>
+        <v>102</v>
       </c>
       <c r="B2" s="2">
         <v>0</v>
@@ -2600,7 +3049,7 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>166</v>
+        <v>104</v>
       </c>
       <c r="B3" s="2">
         <v>0</v>
@@ -2644,7 +3093,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>167</v>
+        <v>106</v>
       </c>
       <c r="B4" s="2">
         <v>0</v>
@@ -2695,209 +3144,167 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="42" customWidth="1"/>
-    <col min="2" max="4" width="14" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>171</v>
+      <c r="A1" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>173</v>
+        <v>35</v>
+      </c>
+      <c r="B2" s="2">
+        <v>100</v>
+      </c>
+      <c r="C2" s="2">
+        <v>100</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>176</v>
+        <v>38</v>
+      </c>
+      <c r="B3" s="2">
+        <v>100</v>
+      </c>
+      <c r="C3" s="2">
+        <v>100</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>178</v>
+        <v>337</v>
+      </c>
+      <c r="B4" s="2">
+        <v>100</v>
+      </c>
+      <c r="C4" s="2">
+        <v>100</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>180</v>
+        <v>338</v>
+      </c>
+      <c r="B5" s="2">
+        <v>100</v>
+      </c>
+      <c r="C5" s="2">
+        <v>100</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>182</v>
+        <v>339</v>
+      </c>
+      <c r="B6" s="2">
+        <v>100</v>
+      </c>
+      <c r="C6" s="2">
+        <v>100</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="B7" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B7" s="2">
+        <v>100</v>
+      </c>
+      <c r="C7" s="2">
+        <v>100</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>186</v>
+        <v>341</v>
+      </c>
+      <c r="B8" s="2">
+        <v>100</v>
+      </c>
+      <c r="C8" s="2">
+        <v>100</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>188</v>
+        <v>342</v>
+      </c>
+      <c r="B9" s="2">
+        <v>100</v>
+      </c>
+      <c r="C9" s="2">
+        <v>100</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>190</v>
+        <v>343</v>
+      </c>
+      <c r="B10" s="2">
+        <v>100</v>
+      </c>
+      <c r="C10" s="2">
+        <v>100</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>193</v>
+        <v>44</v>
+      </c>
+      <c r="B11" s="2">
+        <v>100</v>
+      </c>
+      <c r="C11" s="2">
+        <v>100</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -2909,487 +3316,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="B2" s="2">
-        <v>100</v>
-      </c>
-      <c r="C2" s="2">
-        <v>100</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="B3" s="2">
-        <v>100</v>
-      </c>
-      <c r="C3" s="2">
-        <v>100</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="B4" s="2">
-        <v>100</v>
-      </c>
-      <c r="C4" s="2">
-        <v>100</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="B5" s="2">
-        <v>100</v>
-      </c>
-      <c r="C5" s="2">
-        <v>100</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="B6" s="2">
-        <v>100</v>
-      </c>
-      <c r="C6" s="2">
-        <v>100</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="B7" s="2">
-        <v>100</v>
-      </c>
-      <c r="C7" s="2">
-        <v>100</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="B8" s="2">
-        <v>100</v>
-      </c>
-      <c r="C8" s="2">
-        <v>100</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="B9" s="2">
-        <v>100</v>
-      </c>
-      <c r="C9" s="2">
-        <v>100</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="B10" s="2">
-        <v>100</v>
-      </c>
-      <c r="C10" s="2">
-        <v>100</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="B11" s="2">
-        <v>100</v>
-      </c>
-      <c r="C11" s="2">
-        <v>100</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="E2" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="E3" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="E4" s="2">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="E5" s="2">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="E6" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="E7" s="2">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="E8" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="E9" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="E10" s="2">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="E11" s="2">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="E12" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="E13" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="E14" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="E15" s="2">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="E16" s="2">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="E17" s="2">
-        <v>78</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -3403,58 +3330,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>268</v>
+      <c r="A1" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="O1" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="P1" s="9" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>269</v>
+        <v>360</v>
       </c>
       <c r="B2" s="2">
         <v>0</v>
@@ -3466,7 +3393,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>270</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2">
         <v>0</v>
@@ -3504,7 +3431,7 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>271</v>
+        <v>361</v>
       </c>
       <c r="B3" s="2">
         <v>0.356</v>
@@ -3516,7 +3443,7 @@
         <v>8.36</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>272</v>
+        <v>362</v>
       </c>
       <c r="F3" s="2">
         <v>0.59</v>
@@ -3554,7 +3481,7 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>273</v>
+        <v>363</v>
       </c>
       <c r="B4" s="2">
         <v>1.917</v>
@@ -3566,7 +3493,7 @@
         <v>15.27</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>274</v>
+        <v>364</v>
       </c>
       <c r="F4" s="2">
         <v>3.79</v>
@@ -3604,7 +3531,7 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>275</v>
+        <v>365</v>
       </c>
       <c r="B5" s="2">
         <v>0.955</v>
@@ -3616,7 +3543,7 @@
         <v>16.23</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>270</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2">
         <v>5.38</v>
@@ -3654,7 +3581,7 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>276</v>
+        <v>366</v>
       </c>
       <c r="B6" s="2">
         <v>1.08</v>
@@ -3666,7 +3593,7 @@
         <v>17.31</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>270</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
         <v>7.18</v>
@@ -3704,7 +3631,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>277</v>
+        <v>367</v>
       </c>
       <c r="B7" s="2">
         <v>2.201</v>
@@ -3716,7 +3643,7 @@
         <v>19.51</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>270</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2">
         <v>10.85</v>
@@ -3754,7 +3681,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>278</v>
+        <v>368</v>
       </c>
       <c r="B8" s="2">
         <v>1.604</v>
@@ -3766,7 +3693,7 @@
         <v>22.11</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>279</v>
+        <v>369</v>
       </c>
       <c r="F8" s="2">
         <v>13.52</v>
@@ -3804,7 +3731,7 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>280</v>
+        <v>370</v>
       </c>
       <c r="B9" s="2">
         <v>1.282</v>
@@ -3816,7 +3743,7 @@
         <v>23.4</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>270</v>
+        <v>1</v>
       </c>
       <c r="F9" s="2">
         <v>15.66</v>
@@ -3854,7 +3781,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>281</v>
+        <v>371</v>
       </c>
       <c r="B10" s="2">
         <v>1.304</v>
@@ -3866,7 +3793,7 @@
         <v>25.7</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>282</v>
+        <v>372</v>
       </c>
       <c r="F10" s="2">
         <v>17.83</v>
@@ -3904,7 +3831,7 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>283</v>
+        <v>373</v>
       </c>
       <c r="B11" s="2">
         <v>3.504</v>
@@ -3916,7 +3843,7 @@
         <v>29.2</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>270</v>
+        <v>1</v>
       </c>
       <c r="F11" s="2">
         <v>23.67</v>
@@ -3954,7 +3881,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>284</v>
+        <v>374</v>
       </c>
       <c r="B12" s="2">
         <v>2.12</v>
@@ -3966,7 +3893,7 @@
         <v>31.32</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>270</v>
+        <v>1</v>
       </c>
       <c r="F12" s="2">
         <v>27.21</v>
@@ -4004,7 +3931,7 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>285</v>
+        <v>375</v>
       </c>
       <c r="B13" s="2">
         <v>2.253</v>
@@ -4016,7 +3943,7 @@
         <v>33.58</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>270</v>
+        <v>1</v>
       </c>
       <c r="F13" s="2">
         <v>30.96</v>
@@ -4054,7 +3981,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>286</v>
+        <v>376</v>
       </c>
       <c r="B14" s="2">
         <v>2.145</v>
@@ -4066,7 +3993,7 @@
         <v>36.72</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>287</v>
+        <v>377</v>
       </c>
       <c r="F14" s="2">
         <v>34.54</v>
@@ -4104,7 +4031,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>288</v>
+        <v>378</v>
       </c>
       <c r="B15" s="2">
         <v>5.743</v>
@@ -4116,7 +4043,7 @@
         <v>45.46</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>289</v>
+        <v>379</v>
       </c>
       <c r="F15" s="2">
         <v>44.11</v>
@@ -4154,7 +4081,7 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>290</v>
+        <v>380</v>
       </c>
       <c r="B16" s="2">
         <v>4.281</v>
@@ -4166,7 +4093,7 @@
         <v>49.75</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>270</v>
+        <v>1</v>
       </c>
       <c r="F16" s="2">
         <v>51.24</v>
@@ -4204,7 +4131,7 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>291</v>
+        <v>381</v>
       </c>
       <c r="B17" s="2">
         <v>3.023</v>
@@ -4216,7 +4143,7 @@
         <v>52.77</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>270</v>
+        <v>1</v>
       </c>
       <c r="F17" s="2">
         <v>56.28</v>
@@ -4254,7 +4181,7 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>292</v>
+        <v>382</v>
       </c>
       <c r="B18" s="2">
         <v>3.758</v>
@@ -4266,7 +4193,7 @@
         <v>56.53</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>270</v>
+        <v>1</v>
       </c>
       <c r="F18" s="2">
         <v>62.54</v>
@@ -4304,7 +4231,7 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>293</v>
+        <v>383</v>
       </c>
       <c r="B19" s="2">
         <v>3.077</v>
@@ -4316,7 +4243,7 @@
         <v>59.6</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>270</v>
+        <v>1</v>
       </c>
       <c r="F19" s="2">
         <v>67.67</v>
@@ -4354,7 +4281,7 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>294</v>
+        <v>384</v>
       </c>
       <c r="B20" s="2">
         <v>2.386</v>
@@ -4366,7 +4293,7 @@
         <v>64.99</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>295</v>
+        <v>385</v>
       </c>
       <c r="F20" s="2">
         <v>71.65</v>
@@ -4404,7 +4331,7 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>296</v>
+        <v>386</v>
       </c>
       <c r="B21" s="2">
         <v>2.347</v>
@@ -4416,7 +4343,7 @@
         <v>68.84</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>297</v>
+        <v>387</v>
       </c>
       <c r="F21" s="2">
         <v>75.56</v>
@@ -4454,7 +4381,7 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>298</v>
+        <v>388</v>
       </c>
       <c r="B22" s="2">
         <v>2.063</v>
@@ -4466,7 +4393,7 @@
         <v>70.9</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>270</v>
+        <v>1</v>
       </c>
       <c r="F22" s="2">
         <v>79</v>
@@ -4504,7 +4431,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>299</v>
+        <v>389</v>
       </c>
       <c r="B23" s="2">
         <v>2.42</v>
@@ -4516,7 +4443,7 @@
         <v>73.32</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>270</v>
+        <v>1</v>
       </c>
       <c r="F23" s="2">
         <v>83.03</v>
@@ -4554,7 +4481,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>300</v>
+        <v>390</v>
       </c>
       <c r="B24" s="2">
         <v>1.915</v>
@@ -4566,7 +4493,7 @@
         <v>75.24</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>270</v>
+        <v>1</v>
       </c>
       <c r="F24" s="2">
         <v>86.23</v>
@@ -4604,7 +4531,7 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>301</v>
+        <v>391</v>
       </c>
       <c r="B25" s="2">
         <v>1.899</v>
@@ -4616,7 +4543,7 @@
         <v>80.64</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>302</v>
+        <v>392</v>
       </c>
       <c r="F25" s="2">
         <v>89.39</v>
@@ -4654,7 +4581,7 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>303</v>
+        <v>393</v>
       </c>
       <c r="B26" s="2">
         <v>0.743</v>
@@ -4666,7 +4593,7 @@
         <v>81.38</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>270</v>
+        <v>1</v>
       </c>
       <c r="F26" s="2">
         <v>90.63</v>
@@ -4704,7 +4631,7 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>304</v>
+        <v>394</v>
       </c>
       <c r="B27" s="2">
         <v>0.752</v>
@@ -4716,7 +4643,7 @@
         <v>85.13</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>305</v>
+        <v>395</v>
       </c>
       <c r="F27" s="2">
         <v>91.88</v>
@@ -4754,7 +4681,7 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>306</v>
+        <v>396</v>
       </c>
       <c r="B28" s="2">
         <v>0.948</v>
@@ -4766,7 +4693,7 @@
         <v>86.08</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>270</v>
+        <v>1</v>
       </c>
       <c r="F28" s="2">
         <v>93.46</v>
@@ -4804,7 +4731,7 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>307</v>
+        <v>397</v>
       </c>
       <c r="B29" s="2">
         <v>0.917</v>
@@ -4816,7 +4743,7 @@
         <v>86.99</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>270</v>
+        <v>1</v>
       </c>
       <c r="F29" s="2">
         <v>94.99</v>
@@ -4854,7 +4781,7 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>308</v>
+        <v>398</v>
       </c>
       <c r="B30" s="2">
         <v>0.793</v>
@@ -4866,7 +4793,7 @@
         <v>87.79</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>270</v>
+        <v>1</v>
       </c>
       <c r="F30" s="2">
         <v>96.31</v>
@@ -4904,7 +4831,7 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>309</v>
+        <v>399</v>
       </c>
       <c r="B31" s="2">
         <v>0.575</v>
@@ -4916,7 +4843,7 @@
         <v>93.36</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>310</v>
+        <v>400</v>
       </c>
       <c r="F31" s="2">
         <v>97.27</v>
@@ -4954,7 +4881,7 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>311</v>
+        <v>401</v>
       </c>
       <c r="B32" s="2">
         <v>0.589</v>
@@ -4966,7 +4893,7 @@
         <v>93.95</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>270</v>
+        <v>1</v>
       </c>
       <c r="F32" s="2">
         <v>98.25</v>
@@ -5004,7 +4931,7 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>312</v>
+        <v>402</v>
       </c>
       <c r="B33" s="2">
         <v>0.506</v>
@@ -5016,7 +4943,7 @@
         <v>99.46</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>313</v>
+        <v>403</v>
       </c>
       <c r="F33" s="2">
         <v>99.1</v>
@@ -5054,7 +4981,7 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>314</v>
+        <v>404</v>
       </c>
       <c r="B34" s="2">
         <v>0.446</v>
@@ -5066,7 +4993,7 @@
         <v>99.9</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>270</v>
+        <v>1</v>
       </c>
       <c r="F34" s="2">
         <v>99.84</v>
@@ -5104,7 +5031,7 @@
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>315</v>
+        <v>405</v>
       </c>
       <c r="B35" s="2">
         <v>0.096</v>
@@ -5116,7 +5043,7 @@
         <v>100</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>270</v>
+        <v>1</v>
       </c>
       <c r="F35" s="2">
         <v>100</v>
@@ -5154,7 +5081,7 @@
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>316</v>
+        <v>406</v>
       </c>
       <c r="B36" s="2">
         <v>0</v>
@@ -5166,7 +5093,7 @@
         <v>100</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>270</v>
+        <v>1</v>
       </c>
       <c r="F36" s="2">
         <v>100</v>
@@ -5204,7 +5131,7 @@
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>317</v>
+        <v>407</v>
       </c>
       <c r="B37" s="2">
         <v>0</v>
@@ -5216,7 +5143,7 @@
         <v>100</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>270</v>
+        <v>1</v>
       </c>
       <c r="F37" s="2">
         <v>100</v>
@@ -5250,6 +5177,1640 @@
       </c>
       <c r="P37" s="2">
         <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="C2" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="C3" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="C4" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="C5" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="C6" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="C8" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="C9" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="C11" s="2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="4" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="12" max="12" width="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="4">
+        <f>IFERROR(ROUND(SUMPRODUCT($C$4:$C$1000,$H$4:$H$1000)/SUM($C$4:$C$1000),1),0)</f>
+        <v>100</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="8">
+        <v>40</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" s="8">
+        <v>100</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="8">
+        <v>30</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="8">
+        <v>100</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="8">
+        <v>20</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="8">
+        <v>100</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="8">
+        <v>10</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="8">
+        <v>100</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:N7"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="4" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="12" max="14" width="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="4">
+        <f>IFERROR(ROUND(SUMPRODUCT($C$4:$C$1000,$H$4:$H$1000)/SUM($C$4:$C$1000),1),0)</f>
+        <v>93</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="8">
+        <v>40</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" s="8">
+        <v>100</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7">
+        <v>14000</v>
+      </c>
+      <c r="M4" s="7">
+        <v>99.3</v>
+      </c>
+      <c r="N4" s="7">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="8">
+        <v>30</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="7"/>
+      <c r="H5" s="8">
+        <v>95</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7">
+        <v>11000</v>
+      </c>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="8">
+        <v>20</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="7"/>
+      <c r="H6" s="8">
+        <v>90</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7">
+        <v>7000</v>
+      </c>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" s="8">
+        <v>10</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="7"/>
+      <c r="H7" s="8">
+        <v>65</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7">
+        <v>3300</v>
+      </c>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="4" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="12" max="13" width="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="4">
+        <f>IFERROR(ROUND(SUMPRODUCT($C$4:$C$1000,$H$4:$H$1000)/SUM($C$4:$C$1000),1),0)</f>
+        <v>48</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="8">
+        <v>40</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="7"/>
+      <c r="H4" s="8">
+        <v>60</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="M4" s="7">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="8">
+        <v>30</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="7"/>
+      <c r="H5" s="8">
+        <v>50</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="8">
+        <v>20</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="7"/>
+      <c r="H6" s="8">
+        <v>40</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="8">
+        <v>10</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="7"/>
+      <c r="H7" s="8">
+        <v>10</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:N7"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="4" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="12" max="14" width="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="4">
+        <f>IFERROR(ROUND(SUMPRODUCT($C$4:$C$1000,$H$4:$H$1000)/SUM($C$4:$C$1000),1),0)</f>
+        <v>30.5</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="8">
+        <v>40</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="7"/>
+      <c r="H4" s="8">
+        <v>40</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7">
+        <v>19</v>
+      </c>
+      <c r="M4" s="7">
+        <v>45</v>
+      </c>
+      <c r="N4" s="7">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" s="8">
+        <v>30</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="7"/>
+      <c r="H5" s="8">
+        <v>30</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" s="8">
+        <v>20</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="7"/>
+      <c r="H6" s="8">
+        <v>15</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C7" s="8">
+        <v>10</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="7"/>
+      <c r="H7" s="8">
+        <v>25</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="4" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="12" max="13" width="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="4">
+        <f>IFERROR(ROUND(SUMPRODUCT($C$4:$C$1000,$H$4:$H$1000)/SUM($C$4:$C$1000),1),0)</f>
+        <v>3</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" s="8">
+        <v>40</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="7"/>
+      <c r="H4" s="8">
+        <v>5</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="M4" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" s="8">
+        <v>30</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="7"/>
+      <c r="H5" s="8">
+        <v>2</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M5" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="8">
+        <v>20</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="8">
+        <v>0</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="M6" s="7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="8">
+        <v>10</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="7"/>
+      <c r="H7" s="8">
+        <v>4</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2" s="7">
+        <v>0</v>
+      </c>
+      <c r="D2" s="7">
+        <v>780</v>
+      </c>
+      <c r="E2" s="7">
+        <v>3</v>
+      </c>
+      <c r="F2" s="7"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3" s="7">
+        <v>0</v>
+      </c>
+      <c r="D3" s="7">
+        <v>820</v>
+      </c>
+      <c r="E3" s="7">
+        <v>2</v>
+      </c>
+      <c r="F3" s="7"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C4" s="7">
+        <v>0</v>
+      </c>
+      <c r="D4" s="7">
+        <v>890</v>
+      </c>
+      <c r="E4" s="7">
+        <v>1</v>
+      </c>
+      <c r="F4" s="7"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E2" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E3" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E4" s="2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E5" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E6" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E7" s="2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E8" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E9" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E10" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E11" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E12" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E13" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E14" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E15" s="2">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E16" s="2">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E17" s="2">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -5263,132 +6824,207 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="1" max="1" width="42" customWidth="1"/>
+    <col min="2" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="C2" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="C3" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="C4" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="C5" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="C6" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="C7" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="C8" s="2">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>266</v>
-      </c>
       <c r="B9" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="C9" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>267</v>
+        <v>170</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="C10" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>268</v>
+        <v>173</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C11" s="2">
-        <v>1</v>
+        <v>121</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>172</v>
       </c>
     </row>
   </sheetData>
